--- a/exports/trend_1d/APOLLOHOSP_full_report.xlsx
+++ b/exports/trend_1d/APOLLOHOSP_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:U89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>5.86</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>1263.3</v>
+        <v>1232.4</v>
       </c>
       <c r="I2" t="n">
         <v>1251.703432847077</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>10.05</v>
+        <v>7.36</v>
       </c>
       <c r="L2" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.74</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4.37</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>12.61</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42065</v>
+        <v>42066</v>
       </c>
       <c r="H3" t="n">
-        <v>1348.1</v>
+        <v>1404.3</v>
       </c>
       <c r="I3" t="n">
         <v>1367.821724470357</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.390000000000001</v>
+        <v>-13.95</v>
       </c>
       <c r="L3" t="n">
-        <v>12.24</v>
+        <v>14.65</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>11.48</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42111</v>
+        <v>42114</v>
       </c>
       <c r="H4" t="n">
-        <v>1318.3</v>
+        <v>1279.75</v>
       </c>
       <c r="I4" t="n">
         <v>1309.643403762338</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.12</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.07</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>1.33</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.53</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42184</v>
+        <v>42185</v>
       </c>
       <c r="H5" t="n">
-        <v>1283.25</v>
+        <v>1315.95</v>
       </c>
       <c r="I5" t="n">
         <v>1312.764298406318</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.27</v>
+        <v>-2.83</v>
       </c>
       <c r="L5" t="n">
         <v>4.16</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.61</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H6" t="n">
-        <v>1363.1</v>
+        <v>1336.75</v>
       </c>
       <c r="I6" t="n">
         <v>1340.723090787281</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" t="n">
-        <v>3.58</v>
+        <v>1.58</v>
       </c>
       <c r="L6" t="n">
         <v>2.74</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>11.73</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42256</v>
+        <v>42257</v>
       </c>
       <c r="H7" t="n">
-        <v>1353</v>
+        <v>1410.65</v>
       </c>
       <c r="I7" t="n">
         <v>1401.23251712599</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.22</v>
+        <v>-5.53</v>
       </c>
       <c r="L7" t="n">
-        <v>4.72</v>
+        <v>6.23</v>
       </c>
       <c r="M7" t="n">
         <v>3.64</v>
       </c>
       <c r="N7" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="O7" t="n">
         <v>-1.93</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>16.97</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42304</v>
+        <v>42305</v>
       </c>
       <c r="H8" t="n">
-        <v>1379.35</v>
+        <v>1344.35</v>
       </c>
       <c r="I8" t="n">
         <v>1346.988479072464</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.22</v>
+        <v>-4.7</v>
       </c>
       <c r="L8" t="n">
         <v>6.77</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42339</v>
+        <v>42340</v>
       </c>
       <c r="H9" t="n">
-        <v>1340.45</v>
+        <v>1379.35</v>
       </c>
       <c r="I9" t="n">
         <v>1365.354393284432</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K9" t="n">
-        <v>0.29</v>
+        <v>-2.6</v>
       </c>
       <c r="L9" t="n">
-        <v>2.36</v>
+        <v>3.17</v>
       </c>
       <c r="M9" t="n">
         <v>0.89</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.94</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42377</v>
+        <v>42380</v>
       </c>
       <c r="H10" t="n">
-        <v>1404.55</v>
+        <v>1360.85</v>
       </c>
       <c r="I10" t="n">
         <v>1373.525181640565</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K10" t="n">
-        <v>1.83</v>
+        <v>-1.34</v>
       </c>
       <c r="L10" t="n">
         <v>2.85</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.1</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42398</v>
+        <v>42401</v>
       </c>
       <c r="H11" t="n">
-        <v>1473</v>
+        <v>1498.4</v>
       </c>
       <c r="I11" t="n">
         <v>1473.552652199381</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.24</v>
+        <v>-10.11</v>
       </c>
       <c r="L11" t="n">
-        <v>9.18</v>
+        <v>10.75</v>
       </c>
       <c r="M11" t="n">
         <v>1.75</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.16</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42443</v>
+        <v>42444</v>
       </c>
       <c r="H12" t="n">
-        <v>1408.3</v>
+        <v>1354.2</v>
       </c>
       <c r="I12" t="n">
         <v>1380.109654283485</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.01</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>10.57</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.34</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42517</v>
+        <v>42520</v>
       </c>
       <c r="H13" t="n">
-        <v>1348.2</v>
+        <v>1399.05</v>
       </c>
       <c r="I13" t="n">
         <v>1388.470950832904</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K13" t="n">
-        <v>0.44</v>
+        <v>-3.31</v>
       </c>
       <c r="L13" t="n">
         <v>4.93</v>
@@ -1182,7 +1337,7 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>3.77</v>
       </c>
       <c r="O13" t="n">
         <v>-3.84</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.76</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42622</v>
+        <v>42625</v>
       </c>
       <c r="H14" t="n">
-        <v>1353.1</v>
+        <v>1312.95</v>
       </c>
       <c r="I14" t="n">
         <v>1320.778863277332</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.28</v>
+        <v>-6.15</v>
       </c>
       <c r="L14" t="n">
         <v>9.380000000000001</v>
@@ -1239,7 +1406,7 @@
         <v>2.47</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="O14" t="n">
         <v>3.77</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>7.89</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42660</v>
+        <v>42661</v>
       </c>
       <c r="H15" t="n">
-        <v>1349.05</v>
+        <v>1378.15</v>
       </c>
       <c r="I15" t="n">
         <v>1373.279032622488</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.75</v>
+        <v>-4.97</v>
       </c>
       <c r="L15" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="M15" t="n">
         <v>1.5</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>7.99</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42676</v>
+        <v>42677</v>
       </c>
       <c r="H16" t="n">
-        <v>1301.35</v>
+        <v>1279.45</v>
       </c>
       <c r="I16" t="n">
         <v>1283.662858597588</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.57</v>
+        <v>-7.16</v>
       </c>
       <c r="L16" t="n">
-        <v>5.67</v>
+        <v>7.38</v>
       </c>
       <c r="M16" t="n">
         <v>1.26</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.03</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42738</v>
+        <v>42739</v>
       </c>
       <c r="H17" t="n">
-        <v>1205.45</v>
+        <v>1220.95</v>
       </c>
       <c r="I17" t="n">
         <v>1212.032490616003</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K17" t="n">
-        <v>5.78</v>
+        <v>4.57</v>
       </c>
       <c r="L17" t="n">
         <v>4.03</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.83</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42803</v>
+        <v>42804</v>
       </c>
       <c r="H18" t="n">
-        <v>1225.5</v>
+        <v>1205.55</v>
       </c>
       <c r="I18" t="n">
         <v>1224.430789257005</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K18" t="n">
-        <v>0.37</v>
+        <v>-1.26</v>
       </c>
       <c r="L18" t="n">
         <v>6.83</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42851</v>
+        <v>42852</v>
       </c>
       <c r="H19" t="n">
-        <v>1217.4</v>
+        <v>1245.4</v>
       </c>
       <c r="I19" t="n">
         <v>1219.416220333532</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.98</v>
+        <v>-3.31</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>5.35</v>
       </c>
       <c r="M19" t="n">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="N19" t="n">
         <v>4.25</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.92</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H20" t="n">
-        <v>1261.05</v>
+        <v>1232.15</v>
       </c>
       <c r="I20" t="n">
         <v>1234.067512722735</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
-        <v>1.26</v>
+        <v>-1.06</v>
       </c>
       <c r="L20" t="n">
         <v>2.42</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>7.78</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42891</v>
+        <v>42892</v>
       </c>
       <c r="H21" t="n">
-        <v>1270.95</v>
+        <v>1306.65</v>
       </c>
       <c r="I21" t="n">
         <v>1296.052609503812</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.15</v>
+        <v>-6.05</v>
       </c>
       <c r="L21" t="n">
-        <v>3.72</v>
+        <v>6.44</v>
       </c>
       <c r="M21" t="n">
         <v>0.92</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.76</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42926</v>
+        <v>42927</v>
       </c>
       <c r="H22" t="n">
-        <v>1248.85</v>
+        <v>1234.3</v>
       </c>
       <c r="I22" t="n">
         <v>1240.326982465424</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.42</v>
+        <v>-5.54</v>
       </c>
       <c r="L22" t="n">
-        <v>5.09</v>
+        <v>5.77</v>
       </c>
       <c r="M22" t="n">
         <v>1.29</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.54</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43012</v>
+        <v>43013</v>
       </c>
       <c r="H23" t="n">
-        <v>1049.25</v>
+        <v>1080.55</v>
       </c>
       <c r="I23" t="n">
         <v>1073.327466988699</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K23" t="n">
-        <v>14.99</v>
+        <v>12.46</v>
       </c>
       <c r="L23" t="n">
         <v>6.94</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>9.44</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43046</v>
+        <v>43047</v>
       </c>
       <c r="H24" t="n">
-        <v>1003.05</v>
+        <v>989</v>
       </c>
       <c r="I24" t="n">
         <v>997.2773075563499</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.17</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>7.36</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>0.6899999999999999</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.49</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43059</v>
+        <v>43060</v>
       </c>
       <c r="H25" t="n">
-        <v>1059.6</v>
+        <v>1107.8</v>
       </c>
       <c r="I25" t="n">
         <v>1060.879491581978</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.14</v>
+        <v>-12.01</v>
       </c>
       <c r="L25" t="n">
-        <v>7.89</v>
+        <v>14.05</v>
       </c>
       <c r="M25" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>3.21</v>
+        <v>4.55</v>
       </c>
       <c r="O25" t="n">
         <v>-1.4</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43116</v>
+        <v>43117</v>
       </c>
       <c r="H26" t="n">
-        <v>1147.2</v>
+        <v>1125.7</v>
       </c>
       <c r="I26" t="n">
         <v>1126.357937592905</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K26" t="n">
-        <v>3.56</v>
+        <v>1.62</v>
       </c>
       <c r="L26" t="n">
         <v>4.31</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.18</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43131</v>
+        <v>43132</v>
       </c>
       <c r="H27" t="n">
-        <v>1162.8</v>
+        <v>1218.55</v>
       </c>
       <c r="I27" t="n">
         <v>1207.104640244771</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.3</v>
+        <v>-8.25</v>
       </c>
       <c r="L27" t="n">
-        <v>4.38</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M27" t="n">
         <v>0.91</v>
       </c>
       <c r="N27" t="n">
-        <v>2.58</v>
+        <v>4.79</v>
       </c>
       <c r="O27" t="n">
         <v>-1.87</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.6</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43171</v>
+        <v>43172</v>
       </c>
       <c r="H28" t="n">
-        <v>1129.65</v>
+        <v>1095.9</v>
       </c>
       <c r="I28" t="n">
         <v>1106.830401453557</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.3</v>
+        <v>-10.07</v>
       </c>
       <c r="L28" t="n">
         <v>10.85</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>12.35</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43200</v>
+        <v>43201</v>
       </c>
       <c r="H29" t="n">
-        <v>1086.3</v>
+        <v>1109.55</v>
       </c>
       <c r="I29" t="n">
         <v>1104.368627654326</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K29" t="n">
-        <v>0.88</v>
+        <v>-1.25</v>
       </c>
       <c r="L29" t="n">
         <v>3.16</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>10.55</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43229</v>
+        <v>43230</v>
       </c>
       <c r="H30" t="n">
-        <v>1045.5</v>
+        <v>1024.15</v>
       </c>
       <c r="I30" t="n">
         <v>1034.235792285</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.77</v>
+        <v>-7.7</v>
       </c>
       <c r="L30" t="n">
-        <v>6.12</v>
+        <v>8.07</v>
       </c>
       <c r="M30" t="n">
         <v>0.9</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>10.56</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43266</v>
+        <v>43269</v>
       </c>
       <c r="H31" t="n">
-        <v>1033.25</v>
+        <v>1052.95</v>
       </c>
       <c r="I31" t="n">
         <v>1039.612971659307</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.89</v>
+        <v>-2.81</v>
       </c>
       <c r="L31" t="n">
-        <v>2.81</v>
+        <v>5.08</v>
       </c>
       <c r="M31" t="n">
         <v>1.5</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>10.66</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H32" t="n">
-        <v>974.85</v>
+        <v>940.7</v>
       </c>
       <c r="I32" t="n">
         <v>969.0191717974456</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
-        <v>-7.42</v>
+        <v>-10.66</v>
       </c>
       <c r="L32" t="n">
-        <v>8.119999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
         <v>1.91</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>13.11</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43322</v>
+        <v>43325</v>
       </c>
       <c r="H33" t="n">
-        <v>943.9</v>
+        <v>1068.6</v>
       </c>
       <c r="I33" t="n">
         <v>1021.201392679266</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.34</v>
+        <v>-13.6</v>
       </c>
       <c r="L33" t="n">
-        <v>5.66</v>
+        <v>15.58</v>
       </c>
       <c r="M33" t="n">
         <v>1.45</v>
       </c>
       <c r="N33" t="n">
-        <v>3.89</v>
+        <v>13.21</v>
       </c>
       <c r="O33" t="n">
         <v>-3.5</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>16.36</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H34" t="n">
-        <v>1070.9</v>
+        <v>1044.25</v>
       </c>
       <c r="I34" t="n">
         <v>1066.730734210979</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K34" t="n">
-        <v>0.22</v>
+        <v>-2.28</v>
       </c>
       <c r="L34" t="n">
         <v>11.57</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>13.17</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43404</v>
+        <v>43405</v>
       </c>
       <c r="H35" t="n">
-        <v>1141.05</v>
+        <v>1172.4</v>
       </c>
       <c r="I35" t="n">
         <v>1172.195357864057</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.27</v>
+        <v>-12.27</v>
       </c>
       <c r="L35" t="n">
-        <v>12.62</v>
+        <v>13.48</v>
       </c>
       <c r="M35" t="n">
         <v>0.99</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.46</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43503</v>
+        <v>43504</v>
       </c>
       <c r="H36" t="n">
-        <v>1295.85</v>
+        <v>1257.85</v>
       </c>
       <c r="I36" t="n">
         <v>1259.620860857974</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K36" t="n">
-        <v>10.53</v>
+        <v>7.29</v>
       </c>
       <c r="L36" t="n">
         <v>5.13</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.25</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43553</v>
+        <v>43556</v>
       </c>
       <c r="H37" t="n">
-        <v>1227.6</v>
+        <v>1269.5</v>
       </c>
       <c r="I37" t="n">
         <v>1250.694444263319</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K37" t="n">
-        <v>2.4</v>
+        <v>-0.93</v>
       </c>
       <c r="L37" t="n">
         <v>3.35</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>10.9</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43591</v>
+        <v>43592</v>
       </c>
       <c r="H38" t="n">
-        <v>1190.3</v>
+        <v>1164.95</v>
       </c>
       <c r="I38" t="n">
         <v>1186.707112391885</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.24</v>
+        <v>-8.24</v>
       </c>
       <c r="L38" t="n">
-        <v>9.109999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="M38" t="n">
         <v>2.41</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.66</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43616</v>
+        <v>43619</v>
       </c>
       <c r="H39" t="n">
-        <v>1238.8</v>
+        <v>1357.3</v>
       </c>
       <c r="I39" t="n">
         <v>1247.415857040533</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.34</v>
+        <v>-16.51</v>
       </c>
       <c r="L39" t="n">
-        <v>8.75</v>
+        <v>17.49</v>
       </c>
       <c r="M39" t="n">
         <v>2.58</v>
       </c>
       <c r="N39" t="n">
-        <v>5</v>
+        <v>9.57</v>
       </c>
       <c r="O39" t="n">
         <v>-2.13</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>14.86</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43738</v>
+        <v>43739</v>
       </c>
       <c r="H40" t="n">
-        <v>1395.5</v>
+        <v>1369.25</v>
       </c>
       <c r="I40" t="n">
         <v>1388.28161184338</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K40" t="n">
-        <v>2.81</v>
+        <v>0.88</v>
       </c>
       <c r="L40" t="n">
         <v>8.42</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>11.3</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43755</v>
+        <v>43756</v>
       </c>
       <c r="H41" t="n">
-        <v>1487.3</v>
+        <v>1507.85</v>
       </c>
       <c r="I41" t="n">
         <v>1502.122116252176</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.619999999999999</v>
+        <v>-10.12</v>
       </c>
       <c r="L41" t="n">
-        <v>9.140000000000001</v>
+        <v>11.81</v>
       </c>
       <c r="M41" t="n">
         <v>0.62</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.24</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>43770</v>
+        <v>43773</v>
       </c>
       <c r="H42" t="n">
-        <v>1460</v>
+        <v>1414.75</v>
       </c>
       <c r="I42" t="n">
         <v>1428.18324634712</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.17</v>
+        <v>-6.17</v>
       </c>
       <c r="L42" t="n">
         <v>7.62</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>11.79</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="H43" t="n">
-        <v>1426.35</v>
+        <v>1494.65</v>
       </c>
       <c r="I43" t="n">
         <v>1482.852703701254</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.82</v>
+        <v>-5.65</v>
       </c>
       <c r="L43" t="n">
         <v>6.73</v>
@@ -2892,7 +3407,7 @@
         <v>1.56</v>
       </c>
       <c r="N43" t="n">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="O43" t="n">
         <v>-3.1</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.41</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>43896</v>
+        <v>43899</v>
       </c>
       <c r="H44" t="n">
-        <v>1688.9</v>
+        <v>1640.9</v>
       </c>
       <c r="I44" t="n">
         <v>1651.088439637826</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K44" t="n">
-        <v>13</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L44" t="n">
         <v>4.46</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.03</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44026</v>
+        <v>44027</v>
       </c>
       <c r="H45" t="n">
-        <v>1441.75</v>
+        <v>1465.25</v>
       </c>
       <c r="I45" t="n">
         <v>1460.604709577726</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K45" t="n">
-        <v>12.14</v>
+        <v>10.7</v>
       </c>
       <c r="L45" t="n">
         <v>1.88</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H46" t="n">
-        <v>2919.6</v>
+        <v>2809.35</v>
       </c>
       <c r="I46" t="n">
         <v>2864.507464569105</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K46" t="n">
-        <v>99.26000000000001</v>
+        <v>91.73</v>
       </c>
       <c r="L46" t="n">
         <v>2.57</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>9</v>
+      </c>
+      <c r="U46" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>14.53</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44305</v>
+        <v>44306</v>
       </c>
       <c r="H47" t="n">
-        <v>3157.4</v>
+        <v>3269.65</v>
       </c>
       <c r="I47" t="n">
         <v>3176.880445773269</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.39</v>
+        <v>-16.38</v>
       </c>
       <c r="L47" t="n">
-        <v>15.44</v>
+        <v>17.79</v>
       </c>
       <c r="M47" t="n">
         <v>1.89</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.75</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44463</v>
+        <v>44466</v>
       </c>
       <c r="H48" t="n">
-        <v>4731.8</v>
+        <v>4565.55</v>
       </c>
       <c r="I48" t="n">
         <v>4595.118639487236</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K48" t="n">
-        <v>44.72</v>
+        <v>39.63</v>
       </c>
       <c r="L48" t="n">
         <v>5.33</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>6</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>13.56</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44508</v>
+        <v>44509</v>
       </c>
       <c r="H49" t="n">
-        <v>4405.35</v>
+        <v>4532.9</v>
       </c>
       <c r="I49" t="n">
         <v>4526.013793832091</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K49" t="n">
-        <v>3.51</v>
+        <v>0.72</v>
       </c>
       <c r="L49" t="n">
         <v>4.5</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.91</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44546</v>
+        <v>44547</v>
       </c>
       <c r="H50" t="n">
-        <v>5204.3</v>
+        <v>4786.7</v>
       </c>
       <c r="I50" t="n">
         <v>5005.755271636156</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K50" t="n">
-        <v>14.81</v>
+        <v>5.6</v>
       </c>
       <c r="L50" t="n">
         <v>2.49</v>
@@ -3291,7 +3890,7 @@
         <v>1.55</v>
       </c>
       <c r="N50" t="n">
-        <v>3.03</v>
+        <v>8.02</v>
       </c>
       <c r="O50" t="n">
         <v>2.9</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>16.95</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44622</v>
+        <v>44623</v>
       </c>
       <c r="H51" t="n">
-        <v>4861.25</v>
+        <v>4917.8</v>
       </c>
       <c r="I51" t="n">
         <v>4891.122381310443</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.56</v>
+        <v>-2.74</v>
       </c>
       <c r="L51" t="n">
         <v>8.630000000000001</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>11.68</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44680</v>
+        <v>44683</v>
       </c>
       <c r="H52" t="n">
-        <v>4454.35</v>
+        <v>4304.75</v>
       </c>
       <c r="I52" t="n">
         <v>4440.61762946593</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K52" t="n">
-        <v>-9.42</v>
+        <v>-12.47</v>
       </c>
       <c r="L52" t="n">
-        <v>9.9</v>
+        <v>12.77</v>
       </c>
       <c r="M52" t="n">
         <v>2.68</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>11.7</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44760</v>
+        <v>44761</v>
       </c>
       <c r="H53" t="n">
-        <v>3947.1</v>
+        <v>4020.2</v>
       </c>
       <c r="I53" t="n">
         <v>4005.023713426759</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K53" t="n">
-        <v>8.31</v>
+        <v>6.61</v>
       </c>
       <c r="L53" t="n">
         <v>3.14</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44791</v>
+        <v>44792</v>
       </c>
       <c r="H54" t="n">
-        <v>4266.65</v>
+        <v>4135.35</v>
       </c>
       <c r="I54" t="n">
         <v>4180.490235221107</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K54" t="n">
-        <v>6.13</v>
+        <v>2.86</v>
       </c>
       <c r="L54" t="n">
         <v>2.41</v>
@@ -3519,7 +4166,7 @@
         <v>1.8</v>
       </c>
       <c r="N54" t="n">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="O54" t="n">
         <v>1.85</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.85</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44809</v>
+        <v>44810</v>
       </c>
       <c r="H55" t="n">
-        <v>4282.55</v>
+        <v>4415.5</v>
       </c>
       <c r="I55" t="n">
         <v>4409.267200737376</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.56</v>
+        <v>-6.77</v>
       </c>
       <c r="L55" t="n">
-        <v>6.35</v>
+        <v>6.93</v>
       </c>
       <c r="M55" t="n">
         <v>0.92</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44830</v>
+        <v>44831</v>
       </c>
       <c r="H56" t="n">
-        <v>4282.7</v>
+        <v>4242.95</v>
       </c>
       <c r="I56" t="n">
         <v>4259.043773490636</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.01</v>
+        <v>-3.91</v>
       </c>
       <c r="L56" t="n">
         <v>5.08</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>11.33</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44879</v>
+        <v>44880</v>
       </c>
       <c r="H57" t="n">
-        <v>4556.7</v>
+        <v>4611.95</v>
       </c>
       <c r="I57" t="n">
         <v>4586.061972285442</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K57" t="n">
-        <v>-7.39</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L57" t="n">
         <v>9.52</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.82</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44925</v>
+        <v>44928</v>
       </c>
       <c r="H58" t="n">
-        <v>4477.6</v>
+        <v>4454.35</v>
       </c>
       <c r="I58" t="n">
         <v>4456.486530511286</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.91</v>
+        <v>-3.42</v>
       </c>
       <c r="L58" t="n">
         <v>6.33</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.68</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44971</v>
+        <v>44972</v>
       </c>
       <c r="H59" t="n">
-        <v>4268.85</v>
+        <v>4487.9</v>
       </c>
       <c r="I59" t="n">
         <v>4459.596386915335</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K59" t="n">
-        <v>4.16</v>
+        <v>-0.75</v>
       </c>
       <c r="L59" t="n">
         <v>1.4</v>
@@ -3804,7 +4511,7 @@
         <v>0.84</v>
       </c>
       <c r="N59" t="n">
-        <v>1.75</v>
+        <v>5.13</v>
       </c>
       <c r="O59" t="n">
         <v>-0.52</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>11.75</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H60" t="n">
-        <v>4310.9</v>
+        <v>4234.35</v>
       </c>
       <c r="I60" t="n">
         <v>4243.382291576572</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.94</v>
+        <v>-5.65</v>
       </c>
       <c r="L60" t="n">
         <v>7.08</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45043</v>
+        <v>45044</v>
       </c>
       <c r="H61" t="n">
-        <v>4417.5</v>
+        <v>4513.7</v>
       </c>
       <c r="I61" t="n">
         <v>4482.148557590916</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.33</v>
+        <v>-6.6</v>
       </c>
       <c r="L61" t="n">
-        <v>6.01</v>
+        <v>6.96</v>
       </c>
       <c r="M61" t="n">
         <v>0.76</v>
       </c>
       <c r="N61" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="O61" t="n">
         <v>-1.78</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.12</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45148</v>
+        <v>45149</v>
       </c>
       <c r="H62" t="n">
-        <v>4922.5</v>
+        <v>4906.15</v>
       </c>
       <c r="I62" t="n">
         <v>4919.468061990516</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K62" t="n">
-        <v>9.06</v>
+        <v>8.69</v>
       </c>
       <c r="L62" t="n">
         <v>2.29</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>6.86</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H63" t="n">
-        <v>4985.15</v>
+        <v>5095.95</v>
       </c>
       <c r="I63" t="n">
         <v>5091.989540756696</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.61</v>
+        <v>-3.87</v>
       </c>
       <c r="L63" t="n">
-        <v>2.93</v>
+        <v>4.09</v>
       </c>
       <c r="M63" t="n">
         <v>0.78</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>6.16</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H64" t="n">
-        <v>4859.9</v>
+        <v>4760.3</v>
       </c>
       <c r="I64" t="n">
         <v>4830.768847672332</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.63</v>
+        <v>-6.59</v>
       </c>
       <c r="L64" t="n">
-        <v>5.19</v>
+        <v>7.26</v>
       </c>
       <c r="M64" t="n">
         <v>1.19</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.88</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45232</v>
+        <v>45233</v>
       </c>
       <c r="H65" t="n">
-        <v>4887</v>
+        <v>5153.2</v>
       </c>
       <c r="I65" t="n">
         <v>5087.847420603812</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.66</v>
+        <v>-8.25</v>
       </c>
       <c r="L65" t="n">
-        <v>2.93</v>
+        <v>8.51</v>
       </c>
       <c r="M65" t="n">
-        <v>0.86</v>
+        <v>1.3</v>
       </c>
       <c r="N65" t="n">
-        <v>1.89</v>
+        <v>5.45</v>
       </c>
       <c r="O65" t="n">
         <v>-2.05</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="H66" t="n">
-        <v>6362.35</v>
+        <v>6101.6</v>
       </c>
       <c r="I66" t="n">
         <v>6320.828451767992</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K66" t="n">
-        <v>23.46</v>
+        <v>18.4</v>
       </c>
       <c r="L66" t="n">
         <v>4.19</v>
@@ -4203,7 +4994,7 @@
         <v>1.08</v>
       </c>
       <c r="N66" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O66" t="n">
         <v>5.45</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>10.8</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H67" t="n">
-        <v>6356.8</v>
+        <v>6457.25</v>
       </c>
       <c r="I67" t="n">
         <v>6445.039285676957</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.18</v>
+        <v>-5.83</v>
       </c>
       <c r="L67" t="n">
-        <v>5.93</v>
+        <v>7.46</v>
       </c>
       <c r="M67" t="n">
         <v>1.39</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.92</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="H68" t="n">
-        <v>6258.6</v>
+        <v>5968.35</v>
       </c>
       <c r="I68" t="n">
         <v>6043.92222734155</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.08</v>
+        <v>-7.57</v>
       </c>
       <c r="L68" t="n">
-        <v>6.31</v>
+        <v>11.22</v>
       </c>
       <c r="M68" t="n">
         <v>1.27</v>
       </c>
       <c r="N68" t="n">
-        <v>4.11</v>
+        <v>4.64</v>
       </c>
       <c r="O68" t="n">
         <v>1.58</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.51</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45454</v>
+        <v>45455</v>
       </c>
       <c r="H69" t="n">
-        <v>6107.95</v>
+        <v>6168.6</v>
       </c>
       <c r="I69" t="n">
         <v>6151.826721922875</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.34</v>
+        <v>-3.36</v>
       </c>
       <c r="L69" t="n">
         <v>3.88</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>6.6</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H70" t="n">
-        <v>6905.95</v>
+        <v>6773.6</v>
       </c>
       <c r="I70" t="n">
         <v>6870.761429672164</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K70" t="n">
-        <v>11.95</v>
+        <v>9.81</v>
       </c>
       <c r="L70" t="n">
         <v>1.84</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>7.77</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45602</v>
+        <v>45603</v>
       </c>
       <c r="H71" t="n">
-        <v>6968.1</v>
+        <v>7424.85</v>
       </c>
       <c r="I71" t="n">
         <v>7245.838913492093</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K71" t="n">
-        <v>-2.87</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>5.56</v>
+        <v>10.49</v>
       </c>
       <c r="M71" t="n">
-        <v>0.83</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
-        <v>2.23</v>
+        <v>6.55</v>
       </c>
       <c r="O71" t="n">
         <v>-1.92</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,25 +5387,25 @@
         <v>8.33</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="H72" t="n">
-        <v>7019.55</v>
+        <v>6858.85</v>
       </c>
       <c r="I72" t="n">
         <v>6930.936480163105</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.46</v>
+        <v>-7.62</v>
       </c>
       <c r="L72" t="n">
-        <v>5.96</v>
+        <v>8.01</v>
       </c>
       <c r="M72" t="n">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="N72" t="n">
         <v>3.58</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="H73" t="n">
-        <v>7232.35</v>
+        <v>7274.75</v>
       </c>
       <c r="I73" t="n">
         <v>7234.166034706075</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.45</v>
+        <v>-6.06</v>
       </c>
       <c r="L73" t="n">
-        <v>5.98</v>
+        <v>6.94</v>
       </c>
       <c r="M73" t="n">
         <v>1.26</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>7.43</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H74" t="n">
-        <v>7036.75</v>
+        <v>6839.6</v>
       </c>
       <c r="I74" t="n">
         <v>7015.087038690875</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.27</v>
+        <v>-5.98</v>
       </c>
       <c r="L74" t="n">
-        <v>3.9</v>
+        <v>7.13</v>
       </c>
       <c r="M74" t="n">
         <v>1.24</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>8.07</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H75" t="n">
-        <v>6474.35</v>
+        <v>6611.55</v>
       </c>
       <c r="I75" t="n">
         <v>6477.534210592318</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K75" t="n">
-        <v>5.34</v>
+        <v>3.33</v>
       </c>
       <c r="L75" t="n">
         <v>2.56</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>7.14</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45785</v>
+        <v>45786</v>
       </c>
       <c r="H76" t="n">
-        <v>6851.5</v>
+        <v>6722</v>
       </c>
       <c r="I76" t="n">
         <v>6748.378522184182</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K76" t="n">
-        <v>3.63</v>
+        <v>1.67</v>
       </c>
       <c r="L76" t="n">
         <v>2.74</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>6.91</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="H77" t="n">
-        <v>7101.5</v>
+        <v>7308.5</v>
       </c>
       <c r="I77" t="n">
         <v>7186.616581084876</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K77" t="n">
-        <v>-5.65</v>
+        <v>-8.73</v>
       </c>
       <c r="L77" t="n">
-        <v>6.19</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M77" t="n">
         <v>1.16</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>6.05</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H78" t="n">
-        <v>7359</v>
+        <v>7189.5</v>
       </c>
       <c r="I78" t="n">
         <v>7219.989456789101</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K78" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.63</v>
       </c>
       <c r="L78" t="n">
         <v>2.61</v>
@@ -4887,7 +5822,7 @@
         <v>0.35</v>
       </c>
       <c r="N78" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="O78" t="n">
         <v>2.91</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>6.74</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="H79" t="n">
-        <v>7236.5</v>
+        <v>7808.5</v>
       </c>
       <c r="I79" t="n">
         <v>7515.780471733961</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.65</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>4.85</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="N79" t="n">
-        <v>2.46</v>
+        <v>7.9</v>
       </c>
       <c r="O79" t="n">
         <v>-2.3</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>9.66</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H80" t="n">
-        <v>7624</v>
+        <v>7510</v>
       </c>
       <c r="I80" t="n">
         <v>7556.494250209286</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.36</v>
+        <v>-3.82</v>
       </c>
       <c r="L80" t="n">
         <v>5.37</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,25 +6008,25 @@
         <v>5.04</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="H81" t="n">
-        <v>7671</v>
+        <v>7759</v>
       </c>
       <c r="I81" t="n">
         <v>7758.500752663857</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K81" t="n">
-        <v>-2.14</v>
+        <v>-3.32</v>
       </c>
       <c r="L81" t="n">
-        <v>3.36</v>
+        <v>4.51</v>
       </c>
       <c r="M81" t="n">
-        <v>1.35</v>
+        <v>2.31</v>
       </c>
       <c r="N81" t="n">
         <v>2.85</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>4.68</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H82" t="n">
-        <v>7782</v>
+        <v>7642</v>
       </c>
       <c r="I82" t="n">
         <v>7662.404169406768</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K82" t="n">
-        <v>0.3</v>
+        <v>-1.51</v>
       </c>
       <c r="L82" t="n">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="n">
         <v>1.16</v>
       </c>
       <c r="N82" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="O82" t="n">
         <v>1.15</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>6.99</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H83" t="n">
-        <v>7083</v>
+        <v>7348</v>
       </c>
       <c r="I83" t="n">
         <v>7240.957777160485</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K83" t="n">
-        <v>7.31</v>
+        <v>3.85</v>
       </c>
       <c r="L83" t="n">
         <v>3.26</v>
@@ -5172,7 +6167,7 @@
         <v>0.82</v>
       </c>
       <c r="N83" t="n">
-        <v>1.39</v>
+        <v>3.74</v>
       </c>
       <c r="O83" t="n">
         <v>-1.8</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>3</v>
+      </c>
+      <c r="U83" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>7.09</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H84" t="n">
-        <v>7133</v>
+        <v>6912.5</v>
       </c>
       <c r="I84" t="n">
         <v>7014.107109450141</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K84" t="n">
-        <v>-2.93</v>
+        <v>-5.93</v>
       </c>
       <c r="L84" t="n">
-        <v>5.42</v>
+        <v>6.3</v>
       </c>
       <c r="M84" t="n">
         <v>4.43</v>
       </c>
       <c r="N84" t="n">
-        <v>1.47</v>
+        <v>3.09</v>
       </c>
       <c r="O84" t="n">
         <v>3.74</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5265,28 +6284,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H85" t="n">
-        <v>7219</v>
+        <v>7507</v>
       </c>
       <c r="I85" t="n">
         <v>7232.025116243304</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K85" t="n">
-        <v>-4.43</v>
+        <v>-8.6</v>
       </c>
       <c r="L85" t="n">
-        <v>5.32</v>
+        <v>10.52</v>
       </c>
       <c r="M85" t="n">
-        <v>1.97</v>
+        <v>2.58</v>
       </c>
       <c r="N85" t="n">
-        <v>2.35</v>
+        <v>3.99</v>
       </c>
       <c r="O85" t="n">
         <v>-3.09</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,28 +6353,28 @@
         <v>6.66</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="H86" t="n">
-        <v>7471</v>
+        <v>7252</v>
       </c>
       <c r="I86" t="n">
         <v>7433.456488400455</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.48</v>
+        <v>-3.4</v>
       </c>
       <c r="L86" t="n">
-        <v>1.36</v>
+        <v>3.7</v>
       </c>
       <c r="M86" t="n">
         <v>2.56</v>
       </c>
       <c r="N86" t="n">
-        <v>1.61</v>
+        <v>2.93</v>
       </c>
       <c r="O86" t="n">
         <v>3.99</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5379,22 +6422,22 @@
         <v>7.87</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="H87" t="n">
-        <v>7662</v>
+        <v>7781</v>
       </c>
       <c r="I87" t="n">
         <v>7744.412408833623</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K87" t="n">
-        <v>-5.65</v>
+        <v>-7.29</v>
       </c>
       <c r="L87" t="n">
-        <v>7.58</v>
+        <v>7.76</v>
       </c>
       <c r="M87" t="n">
         <v>1.75</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,19 +6491,19 @@
         <v>7.63</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H88" t="n">
-        <v>8750.5</v>
+        <v>8597</v>
       </c>
       <c r="I88" t="n">
         <v>8623.743827784399</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K88" t="n">
-        <v>12.46</v>
+        <v>10.49</v>
       </c>
       <c r="L88" t="n">
         <v>2.82</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>5</v>
+      </c>
+      <c r="U88" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -5517,6 +6584,14 @@
       <c r="Q89" t="n">
         <v>53</v>
       </c>
+      <c r="R89" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10475,7 +11550,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47.1</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="6">
@@ -10485,7 +11560,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -10495,7 +11570,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
@@ -10505,7 +11580,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10515,7 +11590,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56.5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -10525,7 +11600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99.59999999999999</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="11">
@@ -10535,7 +11610,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -10545,7 +11620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -10555,7 +11630,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.8</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="14">
@@ -10565,7 +11640,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.19</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="15">
@@ -10575,7 +11650,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.81</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -10585,7 +11660,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.49</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="17">
@@ -10595,7 +11670,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>99.26000000000001</v>
+        <v>91.73</v>
       </c>
     </row>
     <row r="18">
@@ -10605,7 +11680,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>37.9</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="19">
@@ -10615,7 +11690,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.48</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="20">
@@ -10625,7 +11700,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.13</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="21">
@@ -10635,7 +11710,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.44</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="22">
@@ -10645,7 +11720,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -10655,7 +11730,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -10665,7 +11740,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="25">
@@ -10685,7 +11760,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="27">
@@ -10705,7 +11780,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
